--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N92_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N92_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>15.15117761958913</v>
+        <v>2.462066363183234</v>
       </c>
       <c r="D2" t="n">
-        <v>15.10265139347413</v>
+        <v>2.454180851439547</v>
       </c>
       <c r="E2" t="n">
-        <v>15.39372834621715</v>
+        <v>2.501480856260287</v>
       </c>
       <c r="F2" t="n">
-        <v>5.929539519761415</v>
+        <v>0.9635501719612303</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>35.03887758087469</v>
+        <v>5.693817606892138</v>
       </c>
       <c r="D3" t="n">
-        <v>26.67286924212788</v>
+        <v>4.334341251845781</v>
       </c>
       <c r="E3" t="n">
-        <v>15.39372834621715</v>
+        <v>2.501480856260287</v>
       </c>
       <c r="F3" t="n">
-        <v>5.929539519761415</v>
+        <v>0.9635501719612303</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>54.45410911951457</v>
+        <v>8.848792731921117</v>
       </c>
       <c r="D4" t="n">
-        <v>17.35167420776424</v>
+        <v>2.819647058761689</v>
       </c>
       <c r="E4" t="n">
-        <v>15.39372834621715</v>
+        <v>2.501480856260287</v>
       </c>
       <c r="F4" t="n">
-        <v>5.929539519761415</v>
+        <v>0.9635501719612303</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>29.40876208397201</v>
+        <v>4.778923838645452</v>
       </c>
       <c r="D5" t="n">
-        <v>10.06230589874905</v>
+        <v>1.635124708546721</v>
       </c>
       <c r="E5" t="n">
-        <v>15.39372834621715</v>
+        <v>2.501480856260287</v>
       </c>
       <c r="F5" t="n">
-        <v>5.929539519761415</v>
+        <v>0.9635501719612303</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>43.6712671086931</v>
+        <v>7.096580905162629</v>
       </c>
       <c r="D6" t="n">
-        <v>19.35933053396574</v>
+        <v>3.145891211769433</v>
       </c>
       <c r="E6" t="n">
-        <v>15.39372834621715</v>
+        <v>2.501480856260287</v>
       </c>
       <c r="F6" t="n">
-        <v>5.929539519761415</v>
+        <v>0.9635501719612303</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>61.10401809659384</v>
+        <v>9.9294029406965</v>
       </c>
       <c r="D7" t="n">
-        <v>26.36928783421318</v>
+        <v>4.285009273059642</v>
       </c>
       <c r="E7" t="n">
-        <v>15.39372834621715</v>
+        <v>2.501480856260287</v>
       </c>
       <c r="F7" t="n">
-        <v>5.929539519761415</v>
+        <v>0.9635501719612303</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
